--- a/goyang-jichuk-road/Worker Output Report.xlsx
+++ b/goyang-jichuk-road/Worker Output Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dj\Desktop\앱개발\안전출력관리4\site-gangbyeon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dj\Desktop\앱개발\안전출력관리4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6363A505-8E57-4EBC-9973-BE204F82F730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B5DE12-DA53-4871-BC00-7278D37940FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="출역장" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>현장명 : 강변아이파크</t>
+    <t>현장명 : 고양지축지구 도로공사 현장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -944,7 +944,7 @@
       <c r="AE3" s="23"/>
       <c r="AN3" s="24">
         <f ca="1">TODAY()</f>
-        <v>46062</v>
+        <v>46084</v>
       </c>
       <c r="AO3" s="25"/>
       <c r="AP3" s="25"/>
